--- a/template.xlsx
+++ b/template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
   <si>
     <t xml:space="preserve">MONTHLY SALARY CERTIFICATE</t>
   </si>
@@ -46,7 +46,7 @@
     <t xml:space="preserve">DESIGNATION</t>
   </si>
   <si>
-    <t xml:space="preserve"> UDISE </t>
+    <t xml:space="preserve">UDISE </t>
   </si>
   <si>
     <t xml:space="preserve">NAME OF SCHOOL</t>
@@ -64,9 +64,6 @@
     <t xml:space="preserve">  PAY SLIP FOR THE MONTH OF :   JULY 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">EMP ID: </t>
-  </si>
-  <si>
     <t xml:space="preserve">EARNINGS</t>
   </si>
   <si>
@@ -121,13 +118,10 @@
     <t xml:space="preserve">G.I.S.</t>
   </si>
   <si>
-    <t xml:space="preserve">q</t>
+    <t xml:space="preserve">DA ARREARS </t>
   </si>
   <si>
     <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DA ARREARS </t>
   </si>
   <si>
     <t xml:space="preserve">REVENUE STAMP</t>
@@ -306,14 +300,14 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -328,20 +322,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.7999"/>
-        <bgColor rgb="FFE8F2E5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE8F2E5"/>
-        <bgColor rgb="FFEBF1DE"/>
+        <bgColor rgb="FFF8E7E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8E7E7"/>
-        <bgColor rgb="FFEBF1DE"/>
+        <bgColor rgb="FFE8F2E5"/>
       </patternFill>
     </fill>
     <fill>
@@ -351,7 +339,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -398,19 +386,6 @@
       <bottom style="thin">
         <color rgb="FF9BB9D6"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FF9BB9D6"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF9BB9D6"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF9BB9D6"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -480,7 +455,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -513,16 +488,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -533,15 +508,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -549,7 +520,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -557,55 +528,47 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -617,7 +580,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -654,7 +617,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFEBF1DE"/>
+      <rgbColor rgb="FFE8F2E5"/>
       <rgbColor rgb="FFF8E7E7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -670,7 +633,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFE8F2E5"/>
+      <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF9BB9D6"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -882,11 +845,11 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.43"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="3.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="4.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.43"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.86"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="1" width="9.14"/>
   </cols>
@@ -984,6 +947,7 @@
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
       <c r="G8" s="9" t="s">
         <v>6</v>
       </c>
@@ -992,7 +956,11 @@
       <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="10" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1003,8 +971,8 @@
       <c r="B10" s="6"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
       <c r="G10" s="6" t="s">
         <v>10</v>
       </c>
@@ -1023,12 +991,12 @@
       <c r="B11" s="6"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
-      <c r="E11" s="6"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
@@ -1047,261 +1015,258 @@
       <c r="E13" s="11"/>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
-      <c r="H13" s="13" t="s">
-        <v>14</v>
-      </c>
+      <c r="H13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14" t="s">
+      <c r="E15" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
+      <c r="B16" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="17" t="s">
+      <c r="G16" s="16"/>
+      <c r="H16" s="17"/>
+    </row>
+    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="17"/>
-      <c r="H16" s="18"/>
-    </row>
-    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="s">
+      <c r="B17" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" s="17" t="s">
+      <c r="G17" s="16"/>
+      <c r="H17" s="17"/>
+    </row>
+    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="17"/>
-      <c r="H17" s="18"/>
-    </row>
-    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
+      <c r="B18" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="19" t="s">
+      <c r="G18" s="19"/>
+      <c r="H18" s="17"/>
+    </row>
+    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="20"/>
-      <c r="H18" s="18"/>
-    </row>
-    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
+      <c r="B19" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="F19" s="19" t="s">
+      <c r="G19" s="19"/>
+      <c r="H19" s="17"/>
+      <c r="N19" s="0"/>
+    </row>
+    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="20"/>
-      <c r="H19" s="18"/>
-    </row>
-    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
+      <c r="B20" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" s="19" t="s">
+      <c r="G20" s="19"/>
+      <c r="H20" s="17"/>
+      <c r="N20" s="0"/>
+    </row>
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="20"/>
-      <c r="H20" s="18"/>
-      <c r="K20" s="1" t="s">
+      <c r="C21" s="20"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="N20" s="21"/>
-    </row>
-    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="22" t="s">
+      <c r="F21" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="G21" s="19"/>
+      <c r="H21" s="17"/>
+      <c r="N21" s="0"/>
+    </row>
+    <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="19" t="s">
+      <c r="B22" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="G21" s="20"/>
-      <c r="H21" s="18"/>
-      <c r="N21" s="17"/>
-    </row>
-    <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22" t="s">
+      <c r="C22" s="16"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="G22" s="16"/>
+      <c r="H22" s="17"/>
+      <c r="N22" s="0"/>
+    </row>
+    <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22" s="17" t="s">
+      <c r="B23" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="G22" s="17"/>
-      <c r="H22" s="18"/>
-      <c r="N22" s="17"/>
-    </row>
-    <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="G23" s="16"/>
+      <c r="H23" s="17"/>
+      <c r="N23" s="0"/>
+    </row>
+    <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="F23" s="17" t="s">
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="F24" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G23" s="17"/>
-      <c r="H23" s="18"/>
-    </row>
-    <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="B24" s="17" t="s">
+      <c r="G24" s="16"/>
+      <c r="H24" s="17"/>
+    </row>
+    <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="F24" s="17" t="s">
+      <c r="G25" s="19"/>
+      <c r="H25" s="17"/>
+    </row>
+    <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="F26" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="G24" s="17"/>
-      <c r="H24" s="18"/>
-    </row>
-    <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="F25" s="19" t="s">
+      <c r="G26" s="19"/>
+      <c r="H26" s="17"/>
+    </row>
+    <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="G25" s="20"/>
-      <c r="H25" s="18"/>
-    </row>
-    <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="26" t="n">
-        <v>11</v>
-      </c>
-      <c r="F26" s="27" t="s">
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="G26" s="20"/>
-      <c r="H26" s="18"/>
-    </row>
-    <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="31"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="28"/>
     </row>
     <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B29" s="5"/>
       <c r="D29" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E29" s="6"/>
     </row>
-    <row r="30" s="34" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="32"/>
+    <row r="30" s="10" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="29"/>
       <c r="C30" s="1"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -1309,9 +1274,9 @@
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
     </row>
-    <row r="31" s="34" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
+    <row r="31" s="10" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="31"/>
+      <c r="B31" s="31"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -1325,61 +1290,63 @@
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
     </row>
-    <row r="32" s="34" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="34" t="s">
+    <row r="32" s="10" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="34" t="s">
+    </row>
+    <row r="33" s="10" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="G32" s="34" t="s">
+      <c r="D33" s="32"/>
+      <c r="G33" s="10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="33" s="34" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="34" t="s">
+    <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D33" s="35"/>
-      <c r="G33" s="34" t="s">
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+    </row>
+    <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="34"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-    </row>
-    <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="34"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1393,14 +1360,15 @@
     <row r="45" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="46" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="32">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:E11"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="E15:G15"/>
@@ -1411,6 +1379,7 @@
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="B23:C23"/>
@@ -1423,6 +1392,7 @@
     <mergeCell ref="E27:G27"/>
     <mergeCell ref="D30:H30"/>
     <mergeCell ref="A31:B31"/>
+    <mergeCell ref="E32:F32"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
